--- a/output/pdf_financials_xlsx/BQE.xlsx
+++ b/output/pdf_financials_xlsx/BQE.xlsx
@@ -8786,7 +8786,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -13167,7 +13167,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -25772,7 +25776,11 @@
           <t>Prepaid and deposits 228,821</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BQE.xlsx
+++ b/output/pdf_financials_xlsx/BQE.xlsx
@@ -1041,16 +1041,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.604385</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.07693</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.079133</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.122418</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0.037983</v>
@@ -1985,16 +1985,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-5.157025</v>
+        <v>-5.76141</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.870677</v>
+        <v>-3.947607</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-10.703954</v>
+        <v>-10.783087</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.618198</v>
+        <v>-4.740616</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-3.215401</v>
@@ -2101,16 +2101,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-5.126053</v>
+        <v>-5.730438</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.839705</v>
+        <v>-3.916635</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-10.672982</v>
+        <v>-10.752115</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.587226</v>
+        <v>-4.709644</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-3.184429</v>
@@ -2159,16 +2159,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-66.03619457158722</v>
+        <v>-73.82216273386504</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-60.04591363201693</v>
+        <v>-61.24895713033545</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-122.0573275861576</v>
+        <v>-122.9623007702101</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-61.87417864287355</v>
+        <v>-63.52539730990746</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-60.50905888976656</v>
@@ -2354,7 +2354,7 @@
         <v>2.491302</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.653465</v>
+        <v>2.491302</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>4.77497</v>
@@ -2375,16 +2375,16 @@
         <v>2.231798</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.984298</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.425312</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.06006</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.943714</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>6.234352</v>
@@ -2470,7 +2470,7 @@
         <v>5.340546</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>7.502709</v>
+        <v>5.340546</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>9.261067000000001</v>
@@ -2491,16 +2491,16 @@
         <v>2.231798</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.984298</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.425312</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.06006</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.943714</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>6.234352</v>
@@ -3187,16 +3187,16 @@
         <v>0.141046</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.027254</v>
+        <v>0.042956</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.512243</v>
+        <v>0.08693099999999999</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.231083</v>
+        <v>0.171023</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.259873</v>
+        <v>0.316159</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.518157</v>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -29285,7 +29285,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -67808,7 +67808,7 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -69683,7 +69683,7 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
@@ -82332,7 +82332,7 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
@@ -85377,7 +85377,7 @@
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
@@ -87296,7 +87296,7 @@
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E791" s="5" t="n">

--- a/output/pdf_financials_xlsx/BQE.xlsx
+++ b/output/pdf_financials_xlsx/BQE.xlsx
@@ -2049,10 +2049,10 @@
         <v>0.030972</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.030972</v>
+        <v>0.8798</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.030972</v>
+        <v>0.69501</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0.030972</v>
@@ -2107,10 +2107,10 @@
         <v>-3.916635</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-10.752115</v>
+        <v>-9.903287000000001</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.709644</v>
+        <v>-4.045606</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-3.184429</v>
@@ -2165,10 +2165,10 @@
         <v>-61.24895713033545</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-122.9623007702101</v>
+        <v>-113.2550158464369</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-63.52539730990746</v>
+        <v>-54.56861038952106</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-60.50905888976656</v>
@@ -6221,22 +6221,22 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.030972</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.030972</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.8798</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.69501</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.030972</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.030972</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
@@ -51804,7 +51804,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -53826,7 +53826,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
           <t>-</t>
@@ -53925,7 +53929,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E456" s="5" t="n">
@@ -73570,7 +73574,7 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -82045,7 +82049,11 @@
           <t>Depreciation of property, plant and equipment (note 8)</t>
         </is>
       </c>
-      <c r="D738" t="inlineStr"/>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E738" t="inlineStr">
         <is>
           <t>-</t>
@@ -82142,7 +82150,7 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
@@ -83591,7 +83599,11 @@
           <t>Depreciation of property, plant and equipment (note 11)</t>
         </is>
       </c>
-      <c r="D754" t="inlineStr"/>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E754" t="inlineStr">
         <is>
           <t>-</t>
@@ -84874,7 +84886,7 @@
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
@@ -86995,7 +87007,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E788" s="5" t="n">

--- a/output/pdf_financials_xlsx/BQE.xlsx
+++ b/output/pdf_financials_xlsx/BQE.xlsx
@@ -1376,10 +1376,10 @@
         <v>0.191221</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>1.275541</v>
+        <v>-1.275541</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>1.6039</v>
+        <v>-1.6039</v>
       </c>
     </row>
     <row r="18">
@@ -2732,19 +2732,19 @@
         <v>0</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.000644</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.022703</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.08611000000000001</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>0.763265</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>0.049006</v>
       </c>
     </row>
     <row r="41">
@@ -2790,19 +2790,19 @@
         <v>1.237261</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>2.009201</v>
+        <v>2.009845</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>3.206869</v>
+        <v>3.229572</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>4.374275</v>
+        <v>4.460385</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>4.46271</v>
+        <v>5.225975</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>5.749554</v>
+        <v>5.79856</v>
       </c>
     </row>
     <row r="42">
@@ -3196,19 +3196,19 @@
         <v>0.171023</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.316159</v>
+        <v>0.315515</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.518157</v>
+        <v>0.495454</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.407717</v>
+        <v>0.321607</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.08122</v>
+        <v>0.317955</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.519443</v>
+        <v>0.470437</v>
       </c>
     </row>
     <row r="49">
@@ -3664,13 +3664,13 @@
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>10048.178</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>10.253288</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>10.155516</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>0</v>
@@ -4511,22 +4511,22 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.104517</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.120039</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.191988</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.105436</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.158419</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.143086</v>
       </c>
     </row>
     <row r="71">
@@ -4569,22 +4569,22 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.104517</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.120039</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.191988</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.105436</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.158419</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.143086</v>
       </c>
     </row>
     <row r="72">
@@ -4801,22 +4801,22 @@
         <v>0.086171</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.252737</v>
+        <v>0.14822</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.59698</v>
+        <v>0.476941</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>1.117437</v>
+        <v>0.925449</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.802548</v>
+        <v>0.697112</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>1.419459</v>
+        <v>1.26104</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>1.23966</v>
+        <v>1.096574</v>
       </c>
     </row>
     <row r="76">
@@ -4977,22 +4977,22 @@
         <v>0</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>0.076516</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>0.086412</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>0.085802</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>0</v>
+        <v>1.500346</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>0</v>
+        <v>1.45103</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>0</v>
+        <v>1.535907</v>
       </c>
     </row>
     <row r="79">
@@ -5035,22 +5035,22 @@
         <v>0</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>0</v>
+        <v>0.076516</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0</v>
+        <v>0.086412</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>0</v>
+        <v>0.085802</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>0</v>
+        <v>1.500346</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>0</v>
+        <v>1.45103</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>0</v>
+        <v>1.535907</v>
       </c>
     </row>
     <row r="80">
@@ -5114,35 +5114,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M80" s="3" t="n">
+        <v>0.02826286416736309</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.01824837648131992</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.02197967748211753</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.1086763594865854</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.07839921414170818</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>0.05830793217609722</v>
       </c>
     </row>
     <row r="81">
@@ -5417,22 +5405,22 @@
         <v>0</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>0.331027</v>
+        <v>0.254511</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>0.777797</v>
+        <v>0.691385</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>0.555167</v>
+        <v>0.469365</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>1.900186</v>
+        <v>0.39984</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>1.841628</v>
+        <v>0.390598</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>2.549074</v>
+        <v>1.013167</v>
       </c>
     </row>
     <row r="86">
@@ -6660,7 +6648,7 @@
         <v>0.110605</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>0.153125</v>
       </c>
       <c r="N107" s="3" t="n">
         <v>0.302749</v>
@@ -7185,10 +7173,10 @@
         <v>0</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="P116" s="3" t="n">
         <v>0</v>
@@ -7481,7 +7469,7 @@
         <v>0</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-0.377772</v>
       </c>
       <c r="Q121" s="3" t="n">
         <v>0</v>
@@ -9946,7 +9934,11 @@
           <t>Lease obligations 14</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10532,7 +10524,11 @@
           <t>Lease obligations 14</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -12268,7 +12264,11 @@
           <t>Lease obligations 13</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -12662,7 +12662,11 @@
           <t>Lease obligations 13</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -13761,7 +13765,11 @@
           <t>Lease obligations 12</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -14163,7 +14171,11 @@
           <t>Lease obligations 12</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -15755,7 +15767,11 @@
           <t>Lease obligations 13</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -16567,7 +16583,11 @@
           <t>Lease obligations 11</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -16862,7 +16882,11 @@
           <t>Lease obligations 11</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -39545,7 +39569,11 @@
           <t>Purchase of intangible assets 8</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -40341,7 +40369,11 @@
           <t>Repurchase of shares 14 (c)</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -41531,7 +41563,11 @@
           <t>Purchase of intangible assets 9</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -43099,7 +43135,11 @@
           <t>Shared-based payment expenses 12</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -45984,7 +46024,11 @@
           <t>Deferred Income tax recovery 17</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -61525,7 +61569,11 @@
           <t>Income tax recovery 19</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr">
         <is>
           <t>-</t>
@@ -63309,7 +63357,11 @@
           <t>Income tax recovery (expense) 18</t>
         </is>
       </c>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr">
         <is>
           <t>-</t>
@@ -70384,7 +70436,11 @@
           <t>Income tax recovery (expense), net 17</t>
         </is>
       </c>
-      <c r="D621" t="inlineStr"/>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E621" t="inlineStr">
         <is>
           <t>-</t>
